--- a/data/ams_weekly_data/Nexlev/ads_report_week17.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week17.xlsx
@@ -7595,7 +7595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7757,10 +7757,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>343.3333333333333</v>
+        <v>343</v>
       </c>
       <c r="E5" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>40.12333333333333</v>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>343.3333333333333</v>
+        <v>343</v>
       </c>
       <c r="E6" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>40.12333333333333</v>
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>343.3333333333333</v>
+        <v>343</v>
       </c>
       <c r="E7" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>40.12333333333333</v>
@@ -8021,19 +8021,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4133.666666666667</v>
+        <v>3665</v>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
-        <v>2746.446666666667</v>
+        <v>2435.228333366786</v>
       </c>
       <c r="G13" t="n">
-        <v>8005.93</v>
+        <v>7098.724256172636</v>
       </c>
       <c r="H13" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8050,23 +8050,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4133.666666666667</v>
+        <v>8736</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="F14" t="n">
-        <v>2746.446666666667</v>
+        <v>5804.111666633215</v>
       </c>
       <c r="G14" t="n">
-        <v>8005.93</v>
+        <v>16919.06574382737</v>
       </c>
       <c r="H14" t="n">
-        <v>2.333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8078,28 +8078,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_SC-05_B0F43P6D23_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4133.666666666667</v>
+        <v>101474</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="F15" t="n">
-        <v>2746.446666666667</v>
+        <v>4639.41</v>
       </c>
       <c r="G15" t="n">
-        <v>8005.93</v>
+        <v>1862.71</v>
       </c>
       <c r="H15" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8111,28 +8111,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>33824.66666666666</v>
+        <v>916</v>
       </c>
       <c r="E16" t="n">
-        <v>63.66666666666666</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>1546.47</v>
+        <v>446.07</v>
       </c>
       <c r="G16" t="n">
-        <v>620.9033333333333</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8144,28 +8144,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33824.66666666666</v>
+        <v>40758</v>
       </c>
       <c r="E17" t="n">
-        <v>63.66666666666666</v>
+        <v>365</v>
       </c>
       <c r="F17" t="n">
-        <v>1546.47</v>
+        <v>9823.25338797823</v>
       </c>
       <c r="G17" t="n">
-        <v>620.9033333333333</v>
+        <v>38544.26091642191</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6666666666666666</v>
+        <v>13</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8177,28 +8177,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33824.66666666666</v>
+        <v>7089</v>
       </c>
       <c r="E18" t="n">
-        <v>63.66666666666666</v>
+        <v>63</v>
       </c>
       <c r="F18" t="n">
-        <v>1546.47</v>
+        <v>1702.989580144072</v>
       </c>
       <c r="G18" t="n">
-        <v>620.9033333333333</v>
+        <v>6719.968626839918</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6666666666666666</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8210,28 +8210,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>916</v>
+        <v>3433</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>446.07</v>
+        <v>824.7245454204074</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3254.349372202905</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8248,23 +8248,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30019.66666666667</v>
+        <v>12251</v>
       </c>
       <c r="E20" t="n">
-        <v>269.3333333333333</v>
+        <v>111</v>
       </c>
       <c r="F20" t="n">
-        <v>7243.38</v>
+        <v>2974.550411938038</v>
       </c>
       <c r="G20" t="n">
-        <v>28364.12333333333</v>
+        <v>11519.39260827775</v>
       </c>
       <c r="H20" t="n">
-        <v>9.333333333333334</v>
+        <v>4</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -8281,23 +8281,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>30019.66666666667</v>
+        <v>26528</v>
       </c>
       <c r="E21" t="n">
-        <v>269.3333333333333</v>
+        <v>238</v>
       </c>
       <c r="F21" t="n">
-        <v>7243.38</v>
+        <v>6404.622074519254</v>
       </c>
       <c r="G21" t="n">
-        <v>28364.12333333333</v>
+        <v>25054.39847625752</v>
       </c>
       <c r="H21" t="n">
-        <v>9.333333333333334</v>
+        <v>8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -8309,28 +8309,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>30019.66666666667</v>
+        <v>659</v>
       </c>
       <c r="E22" t="n">
-        <v>269.3333333333333</v>
+        <v>22</v>
       </c>
       <c r="F22" t="n">
-        <v>7243.38</v>
+        <v>287.0066933849477</v>
       </c>
       <c r="G22" t="n">
-        <v>28364.12333333333</v>
+        <v>761.86</v>
       </c>
       <c r="H22" t="n">
-        <v>9.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8351,19 +8351,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7404</v>
+        <v>9222</v>
       </c>
       <c r="E23" t="n">
-        <v>242.5</v>
+        <v>302</v>
       </c>
       <c r="F23" t="n">
-        <v>3225.06</v>
+        <v>4016.895742822333</v>
       </c>
       <c r="G23" t="n">
-        <v>8560.93</v>
+        <v>10662.86</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8380,23 +8380,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7404</v>
+        <v>4927</v>
       </c>
       <c r="E24" t="n">
-        <v>242.5</v>
+        <v>161</v>
       </c>
       <c r="F24" t="n">
-        <v>3225.06</v>
+        <v>2146.217563792719</v>
       </c>
       <c r="G24" t="n">
-        <v>8560.93</v>
+        <v>5697.14</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>35.33333333333334</v>
+        <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>10.46</v>
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>35.33333333333334</v>
+        <v>35</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>10.46</v>
@@ -8483,10 +8483,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>35.33333333333334</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>10.46</v>
@@ -8516,19 +8516,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>561.5</v>
+        <v>1123</v>
       </c>
       <c r="E28" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="F28" t="n">
-        <v>274.37</v>
+        <v>548.74</v>
       </c>
       <c r="G28" t="n">
-        <v>931.355</v>
+        <v>1862.71</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -8540,28 +8540,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>561.5</v>
+        <v>32936</v>
       </c>
       <c r="E29" t="n">
-        <v>13.5</v>
+        <v>592</v>
       </c>
       <c r="F29" t="n">
-        <v>274.37</v>
+        <v>10874.8278491458</v>
       </c>
       <c r="G29" t="n">
-        <v>931.355</v>
+        <v>55792.8094100033</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5</v>
+        <v>17</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -8578,23 +8578,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>38193</v>
+        <v>3544</v>
       </c>
       <c r="E30" t="n">
-        <v>684</v>
+        <v>62</v>
       </c>
       <c r="F30" t="n">
-        <v>12631.44</v>
+        <v>1184.237229937473</v>
       </c>
       <c r="G30" t="n">
-        <v>63827.09</v>
+        <v>5416.388692183067</v>
       </c>
       <c r="H30" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -8606,28 +8606,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1548</v>
+        <v>1713</v>
       </c>
       <c r="E31" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>539.1</v>
+        <v>572.3749209167299</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2617.891897813619</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -8672,28 +8672,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12045</v>
+        <v>1548</v>
       </c>
       <c r="E33" t="n">
-        <v>540</v>
+        <v>73</v>
       </c>
       <c r="F33" t="n">
-        <v>9952.66</v>
+        <v>539.1</v>
       </c>
       <c r="G33" t="n">
-        <v>51145.77</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8714,19 +8714,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8929.333333333334</v>
+        <v>3489</v>
       </c>
       <c r="E34" t="n">
-        <v>34.33333333333334</v>
+        <v>156</v>
       </c>
       <c r="F34" t="n">
-        <v>645.35</v>
+        <v>2883.329546056529</v>
       </c>
       <c r="G34" t="n">
-        <v>1041.526666666667</v>
+        <v>14817.15539331311</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3333333333333333</v>
+        <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8747,19 +8747,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8929.333333333334</v>
+        <v>7174</v>
       </c>
       <c r="E35" t="n">
-        <v>34.33333333333334</v>
+        <v>322</v>
       </c>
       <c r="F35" t="n">
-        <v>645.35</v>
+        <v>5927.889822973157</v>
       </c>
       <c r="G35" t="n">
-        <v>1041.526666666667</v>
+        <v>30462.86012695358</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3333333333333333</v>
+        <v>8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8780,19 +8780,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8929.333333333334</v>
+        <v>1381</v>
       </c>
       <c r="E36" t="n">
-        <v>34.33333333333334</v>
+        <v>62</v>
       </c>
       <c r="F36" t="n">
-        <v>645.35</v>
+        <v>1141.440630970315</v>
       </c>
       <c r="G36" t="n">
-        <v>1041.526666666667</v>
+        <v>5865.754479733317</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -8804,25 +8804,25 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>45792.5</v>
+        <v>8929</v>
       </c>
       <c r="E37" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="F37" t="n">
-        <v>741.77</v>
+        <v>645.35</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1041.526666666667</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -8837,30 +8837,129 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8929</v>
+      </c>
+      <c r="E38" t="n">
+        <v>34</v>
+      </c>
+      <c r="F38" t="n">
+        <v>645.35</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1041.526666666667</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>8929</v>
+      </c>
+      <c r="E39" t="n">
+        <v>34</v>
+      </c>
+      <c r="F39" t="n">
+        <v>645.35</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1041.526666666667</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>45792</v>
+      </c>
+      <c r="E40" t="n">
+        <v>72</v>
+      </c>
+      <c r="F40" t="n">
+        <v>741.77</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>45792.5</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="D41" t="n">
+        <v>45792</v>
+      </c>
+      <c r="E41" t="n">
         <v>72</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F41" t="n">
         <v>741.77</v>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week17.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week17.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
